--- a/stats_clones_from_01.05.26_live.xlsx
+++ b/stats_clones_from_01.05.26_live.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25225"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26227"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\A. 003 Файлы_ ТЗ_Tech spec_total\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{197B4D09-8521-494B-9993-C2996C5EDCDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96BA04EC-0365-445A-A4B4-737C08665E1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5145" yWindow="840" windowWidth="18900" windowHeight="11655" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3660" yWindow="540" windowWidth="18975" windowHeight="11460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Статистика клонов из Гитхаба_ 2" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -32,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="81">
   <si>
     <t>Проект общий</t>
   </si>
@@ -175,7 +174,106 @@
     <t>01.05.26.</t>
   </si>
   <si>
-    <t>11.08.26.</t>
+    <t>12.08.</t>
+  </si>
+  <si>
+    <t>13.08.</t>
+  </si>
+  <si>
+    <t>14.08.</t>
+  </si>
+  <si>
+    <t>15.08.</t>
+  </si>
+  <si>
+    <t>16.08.</t>
+  </si>
+  <si>
+    <t>17.08.</t>
+  </si>
+  <si>
+    <t>18.08.</t>
+  </si>
+  <si>
+    <t>19.08.</t>
+  </si>
+  <si>
+    <t>20.08.</t>
+  </si>
+  <si>
+    <t>21.08.</t>
+  </si>
+  <si>
+    <t>30.08.</t>
+  </si>
+  <si>
+    <t>31.08.</t>
+  </si>
+  <si>
+    <t>01.09.</t>
+  </si>
+  <si>
+    <t>02.09.</t>
+  </si>
+  <si>
+    <t>03.09.</t>
+  </si>
+  <si>
+    <t>04.09.</t>
+  </si>
+  <si>
+    <t>05.09.</t>
+  </si>
+  <si>
+    <t>06.09.</t>
+  </si>
+  <si>
+    <t>07.09.</t>
+  </si>
+  <si>
+    <t>08.09.</t>
+  </si>
+  <si>
+    <t>09.09.</t>
+  </si>
+  <si>
+    <t>10.09.</t>
+  </si>
+  <si>
+    <t>11.09.</t>
+  </si>
+  <si>
+    <t>12.09.</t>
+  </si>
+  <si>
+    <t>проект</t>
+  </si>
+  <si>
+    <t>ТЗ</t>
+  </si>
+  <si>
+    <t>бланки</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Бланки </t>
+  </si>
+  <si>
+    <t>Бланки</t>
+  </si>
+  <si>
+    <t>13.09.</t>
+  </si>
+  <si>
+    <t>14.09.</t>
+  </si>
+  <si>
+    <t>15.09.</t>
+  </si>
+  <si>
+    <t>16.09.</t>
+  </si>
+  <si>
+    <t>не позже 28.09.26. занести данные</t>
   </si>
 </sst>
 </file>
@@ -728,7 +826,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -773,7 +871,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -838,23 +937,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>104775</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>9526</xdr:rowOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>504825</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>142874</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="TextBox 1">
+        <xdr:cNvPr id="3" name="TextBox 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7DA6E5AF-F3D5-CE09-D25F-1397A5A3BFA3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6F672DAD-5133-4101-801E-7C1259BB0A2C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -862,76 +961,235 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9505950" y="1152526"/>
+          <a:off x="13211175" y="13716000"/>
           <a:ext cx="2943225" cy="2619374"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="lt1"/>
+          <a:sysClr val="window" lastClr="FFFFFF"/>
         </a:solidFill>
         <a:ln w="9525" cmpd="sng">
           <a:solidFill>
-            <a:schemeClr val="lt1">
+            <a:sysClr val="window" lastClr="FFFFFF">
               <a:shade val="50000"/>
-            </a:schemeClr>
+            </a:sysClr>
           </a:solidFill>
         </a:ln>
+        <a:effectLst/>
       </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
       <xdr:txBody>
         <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
         <a:lstStyle/>
         <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
           <a:r>
-            <a:rPr lang="ru-RU" sz="1100"/>
+            <a:rPr kumimoji="0" lang="ru-RU" sz="1100" b="0" i="0" u="none" strike="noStrike" kern="0" cap="none" spc="0" normalizeH="0" baseline="0" noProof="0">
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uLnTx/>
+              <a:uFillTx/>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
             <a:t>Для создания  ярлыка( ссылки в документах, надо нажать на Альт и на файл, который нужно перенести в документы и потом указав на документы отпустить Альт клавишу </a:t>
           </a:r>
         </a:p>
         <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
           <a:r>
-            <a:rPr lang="ru-RU" sz="1100"/>
+            <a:rPr kumimoji="0" lang="ru-RU" sz="1100" b="0" i="0" u="none" strike="noStrike" kern="0" cap="none" spc="0" normalizeH="0" baseline="0" noProof="0">
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uLnTx/>
+              <a:uFillTx/>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
             <a:t> Для автосохранения, нажать на Файл- параметры и - на автосохранение - 5 мин- оптимальный вариант.</a:t>
           </a:r>
         </a:p>
         <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
           <a:r>
-            <a:rPr lang="ru-RU" sz="1100"/>
+            <a:rPr kumimoji="0" lang="ru-RU" sz="1100" b="0" i="0" u="none" strike="noStrike" kern="0" cap="none" spc="0" normalizeH="0" baseline="0" noProof="0">
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uLnTx/>
+              <a:uFillTx/>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
             <a:t>Ручное сохранение:</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
+            <a:rPr kumimoji="0" lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" kern="0" cap="none" spc="0" normalizeH="0" baseline="0" noProof="0">
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uLnTx/>
+              <a:uFillTx/>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
             <a:t> Ctrl +</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="ru-RU" sz="1100"/>
+            <a:rPr kumimoji="0" lang="ru-RU" sz="1100" b="0" i="0" u="none" strike="noStrike" kern="0" cap="none" spc="0" normalizeH="0" baseline="0" noProof="0">
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uLnTx/>
+              <a:uFillTx/>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
             <a:t> </a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
+            <a:rPr kumimoji="0" lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" kern="0" cap="none" spc="0" normalizeH="0" baseline="0" noProof="0">
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uLnTx/>
+              <a:uFillTx/>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
             <a:t>S</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="ru-RU" sz="1100"/>
+            <a:rPr kumimoji="0" lang="ru-RU" sz="1100" b="0" i="0" u="none" strike="noStrike" kern="0" cap="none" spc="0" normalizeH="0" baseline="0" noProof="0">
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uLnTx/>
+              <a:uFillTx/>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
             <a:t> _ этот вариант ещё лучше, не надо ждать 5 минут.  Работает при любой раскладке клавиатуры.</a:t>
           </a:r>
         </a:p>
         <a:p>
-          <a:endParaRPr lang="ru-RU" sz="1100"/>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:endParaRPr kumimoji="0" lang="ru-RU" sz="1100" b="0" i="0" u="none" strike="noStrike" kern="0" cap="none" spc="0" normalizeH="0" baseline="0" noProof="0">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:uLnTx/>
+            <a:uFillTx/>
+            <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -1245,35 +1503,45 @@
     <col min="4" max="4" width="1.85546875" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="11.28515625" customWidth="1"/>
+    <col min="7" max="7" width="2.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1" s="20" t="s">
         <v>16</v>
       </c>
       <c r="B1" s="13">
         <f>B300</f>
-        <v>66</v>
+        <v>140</v>
       </c>
       <c r="C1" s="13">
         <f>C300</f>
-        <v>76</v>
+        <v>119</v>
       </c>
       <c r="D1" s="5"/>
       <c r="E1" s="5">
         <f>E300</f>
-        <v>412</v>
+        <v>524</v>
       </c>
       <c r="F1" s="5">
         <f>F300</f>
-        <v>229</v>
-      </c>
-      <c r="G1" s="12" t="s">
+        <v>311</v>
+      </c>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5">
+        <f t="shared" ref="H1:I1" si="0">H300</f>
+        <v>10</v>
+      </c>
+      <c r="I1" s="5">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="J1" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="H1" s="12"/>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M1" s="12"/>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
         <v>21</v>
       </c>
@@ -1282,8 +1550,32 @@
       <c r="D2" s="19"/>
       <c r="E2" s="19"/>
       <c r="F2" s="19"/>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K2" t="s">
+        <v>71</v>
+      </c>
+      <c r="L2" t="s">
+        <v>73</v>
+      </c>
+      <c r="N2" t="s">
+        <v>71</v>
+      </c>
+      <c r="O2" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>72</v>
+      </c>
+      <c r="R2" t="s">
+        <v>72</v>
+      </c>
+      <c r="S2" t="s">
+        <v>72</v>
+      </c>
+      <c r="T2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B3" s="18" t="s">
         <v>0</v>
       </c>
@@ -1295,11 +1587,17 @@
       <c r="F3" t="s">
         <v>1</v>
       </c>
-      <c r="K3" t="s">
+      <c r="H3" t="s">
+        <v>74</v>
+      </c>
+      <c r="I3" t="s">
+        <v>75</v>
+      </c>
+      <c r="L3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1316,20 +1614,26 @@
       <c r="F4" t="s">
         <v>2</v>
       </c>
-      <c r="J4" t="s">
+      <c r="H4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I4" t="s">
         <v>2</v>
       </c>
       <c r="K4" t="s">
+        <v>2</v>
+      </c>
+      <c r="L4" t="s">
         <v>3</v>
       </c>
-      <c r="M4" t="s">
-        <v>2</v>
-      </c>
       <c r="N4" t="s">
+        <v>2</v>
+      </c>
+      <c r="O4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>3</v>
       </c>
@@ -1343,15 +1647,32 @@
       <c r="F5" t="s">
         <v>4</v>
       </c>
-      <c r="G5" s="1"/>
-      <c r="J5" t="s">
+      <c r="H5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I5" t="s">
+        <v>4</v>
+      </c>
+      <c r="K5" t="s">
         <v>17</v>
       </c>
-      <c r="M5" t="s">
+      <c r="N5" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q5" t="s">
+        <v>2</v>
+      </c>
+      <c r="R5" t="s">
+        <v>3</v>
+      </c>
+      <c r="T5" t="s">
+        <v>2</v>
+      </c>
+      <c r="U5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>46</v>
       </c>
@@ -1372,7 +1693,7 @@
       <c r="M6" s="2"/>
       <c r="N6" s="5"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>19</v>
       </c>
@@ -1393,7 +1714,7 @@
       <c r="M7" s="2"/>
       <c r="N7" s="5"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>46145</v>
       </c>
@@ -1414,7 +1735,7 @@
       <c r="M8" s="3"/>
       <c r="N8" s="5"/>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>46146</v>
       </c>
@@ -1435,7 +1756,7 @@
       <c r="M9" s="3"/>
       <c r="N9" s="5"/>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>46147</v>
       </c>
@@ -1456,7 +1777,7 @@
       <c r="M10" s="4"/>
       <c r="N10" s="5"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>46148</v>
       </c>
@@ -1477,7 +1798,7 @@
       <c r="M11" s="4"/>
       <c r="N11" s="5"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>46149</v>
       </c>
@@ -1496,7 +1817,7 @@
       <c r="J12" s="1"/>
       <c r="M12" s="1"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>46150</v>
       </c>
@@ -1515,7 +1836,7 @@
       <c r="J13" s="1"/>
       <c r="M13" s="1"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>46151</v>
       </c>
@@ -1534,7 +1855,7 @@
       <c r="J14" s="1"/>
       <c r="M14" s="1"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>5</v>
       </c>
@@ -1551,7 +1872,7 @@
       </c>
       <c r="G15" s="3"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>6</v>
       </c>
@@ -2118,7 +2439,7 @@
         <v>1</v>
       </c>
       <c r="D47" s="6"/>
-      <c r="E47" s="20">
+      <c r="E47" s="5">
         <v>1</v>
       </c>
       <c r="F47" s="5">
@@ -2138,7 +2459,7 @@
         <v>0</v>
       </c>
       <c r="D48" s="6"/>
-      <c r="E48" s="20">
+      <c r="E48" s="5">
         <v>2</v>
       </c>
       <c r="F48" s="5">
@@ -2147,7 +2468,7 @@
       <c r="J48" s="1"/>
       <c r="M48" s="1"/>
     </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
         <v>12</v>
       </c>
@@ -2158,7 +2479,7 @@
         <v>1</v>
       </c>
       <c r="D49" s="6"/>
-      <c r="E49" s="20">
+      <c r="E49" s="5">
         <v>2</v>
       </c>
       <c r="F49" s="5">
@@ -2170,7 +2491,7 @@
       <c r="J49" s="1"/>
       <c r="M49" s="1"/>
     </row>
-    <row r="50" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A50" s="4">
         <v>41426</v>
       </c>
@@ -2190,7 +2511,7 @@
       <c r="J50" s="1"/>
       <c r="M50" s="1"/>
     </row>
-    <row r="51" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A51" s="4">
         <v>41791</v>
       </c>
@@ -2210,7 +2531,7 @@
       <c r="J51" s="1"/>
       <c r="M51" s="1"/>
     </row>
-    <row r="52" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A52" s="4">
         <v>42156</v>
       </c>
@@ -2230,7 +2551,7 @@
       <c r="M52" s="2"/>
       <c r="O52" s="2"/>
     </row>
-    <row r="53" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
         <v>41</v>
       </c>
@@ -2247,32 +2568,8 @@
       <c r="F53" s="15">
         <v>4</v>
       </c>
-      <c r="K53" t="s">
-        <v>2</v>
-      </c>
-      <c r="L53" t="s">
-        <v>3</v>
-      </c>
-      <c r="N53" t="s">
-        <v>2</v>
-      </c>
-      <c r="O53" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q53" t="s">
-        <v>2</v>
-      </c>
-      <c r="R53" t="s">
-        <v>3</v>
-      </c>
-      <c r="T53" t="s">
-        <v>2</v>
-      </c>
-      <c r="U53" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="54" spans="1:21" x14ac:dyDescent="0.25">
+    </row>
+    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
         <v>42</v>
       </c>
@@ -2289,33 +2586,13 @@
       <c r="F54" s="15">
         <v>1</v>
       </c>
-      <c r="K54" s="1">
-        <v>47300</v>
-      </c>
-      <c r="L54">
-        <v>0</v>
-      </c>
+      <c r="K54" s="2"/>
       <c r="M54" s="2"/>
-      <c r="N54" s="1">
-        <v>47300</v>
-      </c>
-      <c r="O54">
-        <v>0</v>
-      </c>
-      <c r="Q54" s="1">
-        <v>47300</v>
-      </c>
-      <c r="R54">
-        <v>16</v>
-      </c>
-      <c r="T54" s="1">
-        <v>47300</v>
-      </c>
-      <c r="U54">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="55" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="N54" s="1"/>
+      <c r="Q54" s="2"/>
+      <c r="T54" s="1"/>
+    </row>
+    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A55" s="4">
         <v>43252</v>
       </c>
@@ -2332,33 +2609,12 @@
       <c r="F55" s="15">
         <v>2</v>
       </c>
-      <c r="K55" s="1">
-        <v>11140</v>
-      </c>
-      <c r="L55">
-        <v>0</v>
-      </c>
       <c r="M55" s="2"/>
-      <c r="N55" s="1">
-        <v>11140</v>
-      </c>
-      <c r="O55">
-        <v>0</v>
-      </c>
-      <c r="Q55" s="1">
-        <v>11140</v>
-      </c>
-      <c r="R55">
-        <v>19</v>
-      </c>
-      <c r="T55" s="1">
-        <v>11140</v>
-      </c>
-      <c r="U55">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="56" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="N55" s="1"/>
+      <c r="Q55" s="2"/>
+      <c r="T55" s="1"/>
+    </row>
+    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
         <v>43</v>
       </c>
@@ -2379,33 +2635,12 @@
       <c r="H56" s="5"/>
       <c r="I56" s="5"/>
       <c r="J56" s="5"/>
-      <c r="K56" s="1">
-        <v>11505</v>
-      </c>
-      <c r="L56">
-        <v>0</v>
-      </c>
       <c r="M56" s="1"/>
-      <c r="N56" s="1">
-        <v>11505</v>
-      </c>
-      <c r="O56">
-        <v>0</v>
-      </c>
-      <c r="Q56" s="1">
-        <v>11505</v>
-      </c>
-      <c r="R56">
-        <v>2</v>
-      </c>
-      <c r="T56" s="1">
-        <v>11505</v>
-      </c>
-      <c r="U56">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="57" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="N56" s="2"/>
+      <c r="Q56" s="2"/>
+      <c r="T56" s="1"/>
+    </row>
+    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
         <v>44</v>
       </c>
@@ -2422,33 +2657,13 @@
       <c r="F57" s="15">
         <v>6</v>
       </c>
-      <c r="K57" s="2">
-        <v>46030</v>
-      </c>
-      <c r="L57">
-        <v>0</v>
-      </c>
+      <c r="K57" s="2"/>
       <c r="M57" s="1"/>
-      <c r="N57" s="2">
-        <v>46030</v>
-      </c>
-      <c r="O57">
-        <v>0</v>
-      </c>
-      <c r="Q57" s="2">
-        <v>46030</v>
-      </c>
-      <c r="R57">
-        <v>4</v>
-      </c>
-      <c r="T57" s="2">
-        <v>46030</v>
-      </c>
-      <c r="U57">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="N57" s="2"/>
+      <c r="Q57" s="2"/>
+      <c r="T57" s="1"/>
+    </row>
+    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A58" s="4">
         <v>44348</v>
       </c>
@@ -2465,33 +2680,13 @@
       <c r="F58" s="15">
         <v>1</v>
       </c>
-      <c r="K58" s="2">
-        <v>46061</v>
-      </c>
-      <c r="L58">
-        <v>0</v>
-      </c>
+      <c r="K58" s="2"/>
       <c r="M58" s="1"/>
-      <c r="N58" s="2">
-        <v>46061</v>
-      </c>
-      <c r="O58">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="2">
-        <v>46061</v>
-      </c>
-      <c r="R58">
-        <v>2</v>
-      </c>
-      <c r="T58" s="2">
-        <v>46061</v>
-      </c>
-      <c r="U58">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="N58" s="2"/>
+      <c r="Q58" s="2"/>
+      <c r="T58" s="1"/>
+    </row>
+    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
         <v>45</v>
       </c>
@@ -2508,33 +2703,13 @@
       <c r="F59" s="15">
         <v>4</v>
       </c>
-      <c r="K59" s="2">
-        <v>46089</v>
-      </c>
-      <c r="L59">
-        <v>0</v>
-      </c>
+      <c r="K59" s="1"/>
       <c r="M59" s="1"/>
-      <c r="N59" s="2">
-        <v>46089</v>
-      </c>
-      <c r="O59">
-        <v>0</v>
-      </c>
-      <c r="Q59" s="2">
-        <v>46089</v>
-      </c>
-      <c r="R59">
-        <v>1</v>
-      </c>
-      <c r="T59" s="2">
-        <v>46089</v>
-      </c>
-      <c r="U59">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="N59" s="2"/>
+      <c r="Q59" s="1"/>
+      <c r="T59" s="1"/>
+    </row>
+    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A60" s="4">
         <v>45078</v>
       </c>
@@ -2551,33 +2726,13 @@
       <c r="F60" s="5">
         <v>0</v>
       </c>
-      <c r="K60" s="2">
-        <v>46120</v>
-      </c>
-      <c r="L60">
-        <v>0</v>
-      </c>
+      <c r="K60" s="1"/>
       <c r="M60" s="1"/>
-      <c r="N60" s="2">
-        <v>46120</v>
-      </c>
-      <c r="O60">
-        <v>0</v>
-      </c>
-      <c r="Q60" s="2">
-        <v>46120</v>
-      </c>
-      <c r="R60">
-        <v>0</v>
-      </c>
-      <c r="T60" s="2">
-        <v>46120</v>
-      </c>
-      <c r="U60">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="N60" s="2"/>
+      <c r="Q60" s="1"/>
+      <c r="T60" s="1"/>
+    </row>
+    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A61" s="4">
         <v>45444</v>
       </c>
@@ -2594,33 +2749,13 @@
       <c r="F61" s="15">
         <v>3</v>
       </c>
-      <c r="K61" s="2">
-        <v>46150</v>
-      </c>
-      <c r="L61">
-        <v>0</v>
-      </c>
+      <c r="K61" s="1"/>
       <c r="M61" s="1"/>
-      <c r="N61" s="2">
-        <v>46150</v>
-      </c>
-      <c r="O61">
-        <v>0</v>
-      </c>
-      <c r="Q61" s="2">
-        <v>46150</v>
-      </c>
-      <c r="R61">
-        <v>0</v>
-      </c>
-      <c r="T61" s="2">
-        <v>46150</v>
-      </c>
-      <c r="U61">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="N61" s="2"/>
+      <c r="Q61" s="1"/>
+      <c r="T61" s="1"/>
+    </row>
+    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A62" s="3"/>
       <c r="B62" s="5"/>
       <c r="C62" s="5"/>
@@ -2629,63 +2764,23 @@
       </c>
       <c r="H62" s="14"/>
       <c r="I62" s="14"/>
-      <c r="K62" s="2">
-        <v>46181</v>
-      </c>
-      <c r="L62">
-        <v>0</v>
-      </c>
+      <c r="K62" s="1"/>
       <c r="M62" s="1"/>
-      <c r="N62" s="2">
-        <v>46181</v>
-      </c>
-      <c r="O62">
-        <v>0</v>
-      </c>
-      <c r="Q62" s="2">
-        <v>46181</v>
-      </c>
-      <c r="R62">
-        <v>2</v>
-      </c>
-      <c r="T62" s="2">
-        <v>46181</v>
-      </c>
-      <c r="U62">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="63" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="N62" s="2"/>
+      <c r="Q62" s="1"/>
+      <c r="T62" s="1"/>
+    </row>
+    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A63" s="3"/>
       <c r="B63" s="5"/>
       <c r="C63" s="5"/>
-      <c r="K63" s="2">
-        <v>46211</v>
-      </c>
-      <c r="L63">
-        <v>0</v>
-      </c>
+      <c r="K63" s="1"/>
       <c r="M63" s="1"/>
-      <c r="N63" s="2">
-        <v>46211</v>
-      </c>
-      <c r="O63">
-        <v>0</v>
-      </c>
-      <c r="Q63" s="2">
-        <v>46211</v>
-      </c>
-      <c r="R63">
-        <v>0</v>
-      </c>
-      <c r="T63" s="2">
-        <v>46211</v>
-      </c>
-      <c r="U63">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="N63" s="2"/>
+      <c r="Q63" s="1"/>
+      <c r="T63" s="1"/>
+    </row>
+    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
         <v>33</v>
       </c>
@@ -2697,33 +2792,13 @@
       <c r="F64" s="15">
         <v>10</v>
       </c>
-      <c r="K64" s="2">
-        <v>46242</v>
-      </c>
-      <c r="L64">
-        <v>0</v>
-      </c>
+      <c r="K64" s="1"/>
       <c r="M64" s="1"/>
-      <c r="N64" s="2">
-        <v>46242</v>
-      </c>
-      <c r="O64">
-        <v>0</v>
-      </c>
-      <c r="Q64" s="2">
-        <v>46242</v>
-      </c>
-      <c r="R64">
-        <v>0</v>
-      </c>
-      <c r="T64" s="2">
-        <v>46242</v>
-      </c>
-      <c r="U64">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="N64" s="2"/>
+      <c r="Q64" s="1"/>
+      <c r="T64" s="1"/>
+    </row>
+    <row r="65" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
         <v>34</v>
       </c>
@@ -2735,33 +2810,13 @@
       <c r="F65" s="15">
         <v>10</v>
       </c>
-      <c r="K65" s="2">
-        <v>46273</v>
-      </c>
-      <c r="L65">
-        <v>0</v>
-      </c>
+      <c r="K65" s="1"/>
       <c r="M65" s="1"/>
-      <c r="N65" s="2">
-        <v>46273</v>
-      </c>
-      <c r="O65">
-        <v>0</v>
-      </c>
-      <c r="Q65" s="2">
-        <v>46273</v>
-      </c>
-      <c r="R65">
-        <v>0</v>
-      </c>
-      <c r="T65" s="2">
-        <v>46273</v>
-      </c>
-      <c r="U65">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="N65" s="2"/>
+      <c r="Q65" s="1"/>
+      <c r="T65" s="1"/>
+    </row>
+    <row r="66" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
         <v>35</v>
       </c>
@@ -2773,33 +2828,13 @@
       <c r="F66" s="5">
         <v>2</v>
       </c>
-      <c r="K66" s="2">
-        <v>46303</v>
-      </c>
-      <c r="L66">
-        <v>4</v>
-      </c>
+      <c r="K66" s="1"/>
       <c r="M66" s="1"/>
-      <c r="N66" s="2">
-        <v>46303</v>
-      </c>
-      <c r="O66">
-        <v>4</v>
-      </c>
-      <c r="Q66" s="2">
-        <v>46303</v>
-      </c>
-      <c r="R66">
-        <v>0</v>
-      </c>
-      <c r="T66" s="2">
-        <v>46303</v>
-      </c>
-      <c r="U66">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="N66" s="2"/>
+      <c r="Q66" s="1"/>
+      <c r="T66" s="1"/>
+    </row>
+    <row r="67" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
         <v>23</v>
       </c>
@@ -2811,33 +2846,12 @@
       <c r="F67" s="5">
         <v>3</v>
       </c>
-      <c r="K67" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="L67">
-        <v>34</v>
-      </c>
       <c r="M67" s="1"/>
-      <c r="N67" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="O67">
-        <v>22</v>
-      </c>
-      <c r="Q67" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="R67">
-        <v>26</v>
-      </c>
-      <c r="T67" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="U67">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="68" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="N67" s="2"/>
+      <c r="Q67" s="1"/>
+      <c r="T67" s="1"/>
+    </row>
+    <row r="68" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
         <v>24</v>
       </c>
@@ -2849,8 +2863,9 @@
       <c r="F68" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="69" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="N68" s="1"/>
+    </row>
+    <row r="69" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
         <v>32</v>
       </c>
@@ -2862,8 +2877,9 @@
       <c r="F69" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="70" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="N69" s="1"/>
+    </row>
+    <row r="70" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
         <v>25</v>
       </c>
@@ -2875,8 +2891,9 @@
       <c r="F70" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="N70" s="1"/>
+    </row>
+    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
         <v>26</v>
       </c>
@@ -2888,8 +2905,9 @@
       <c r="F71" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="N71" s="1"/>
+    </row>
+    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
         <v>31</v>
       </c>
@@ -2901,8 +2919,9 @@
       <c r="F72" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="73" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="N72" s="1"/>
+    </row>
+    <row r="73" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
         <v>27</v>
       </c>
@@ -2914,8 +2933,9 @@
       <c r="F73" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="N73" s="1"/>
+    </row>
+    <row r="74" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
         <v>28</v>
       </c>
@@ -2927,8 +2947,9 @@
       <c r="F74" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="N74" s="1"/>
+    </row>
+    <row r="75" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
         <v>29</v>
       </c>
@@ -2940,8 +2961,9 @@
       <c r="F75" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="N75" s="1"/>
+    </row>
+    <row r="76" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
         <v>30</v>
       </c>
@@ -2952,14 +2974,15 @@
         <v>4</v>
       </c>
       <c r="D76" s="15"/>
-      <c r="E76" s="20">
-        <v>0</v>
-      </c>
-      <c r="F76" s="20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="E76" s="5">
+        <v>0</v>
+      </c>
+      <c r="F76" s="5">
+        <v>0</v>
+      </c>
+      <c r="N76" s="1"/>
+    </row>
+    <row r="77" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
         <v>22</v>
       </c>
@@ -2976,385 +2999,1128 @@
       <c r="F77" s="15">
         <v>15</v>
       </c>
-    </row>
-    <row r="78" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A78" s="3"/>
+      <c r="N77" s="2"/>
+    </row>
+    <row r="78" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A78" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B78" s="5">
+        <v>0</v>
+      </c>
+      <c r="C78" s="5">
+        <v>0</v>
+      </c>
       <c r="D78" s="5"/>
-      <c r="E78" s="5"/>
-      <c r="F78" s="5"/>
-    </row>
-    <row r="79" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A79" s="3"/>
+      <c r="E78" s="5">
+        <v>21</v>
+      </c>
+      <c r="F78" s="5">
+        <v>12</v>
+      </c>
+      <c r="N78" s="2"/>
+    </row>
+    <row r="79" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A79" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B79" s="5"/>
+      <c r="C79" s="5">
+        <v>0</v>
+      </c>
       <c r="D79" s="5"/>
-      <c r="E79" s="5"/>
+      <c r="E79" s="5">
+        <v>1</v>
+      </c>
       <c r="F79" s="5"/>
       <c r="G79" s="14" t="s">
         <v>36</v>
       </c>
       <c r="H79" s="14"/>
       <c r="I79" s="14"/>
-    </row>
-    <row r="80" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A80" s="9"/>
-      <c r="B80" s="9"/>
-      <c r="C80" s="5"/>
+      <c r="N79" s="2"/>
+    </row>
+    <row r="80" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A80" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B80" s="5"/>
+      <c r="C80" s="5">
+        <v>1</v>
+      </c>
       <c r="D80" s="5"/>
-      <c r="E80" s="5"/>
+      <c r="E80" s="5">
+        <v>4</v>
+      </c>
       <c r="F80" s="5"/>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A81" s="9"/>
-      <c r="B81" s="9"/>
-      <c r="C81" s="5"/>
+      <c r="N80" s="2"/>
+    </row>
+    <row r="81" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A81" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B81" s="5"/>
+      <c r="C81" s="5">
+        <v>0</v>
+      </c>
       <c r="D81" s="5"/>
-      <c r="E81" s="5"/>
+      <c r="E81" s="5">
+        <v>0</v>
+      </c>
       <c r="F81" s="5"/>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A82" s="9"/>
-      <c r="B82" s="9"/>
-      <c r="C82" s="5"/>
+      <c r="G81" s="5"/>
+      <c r="H81" s="5"/>
+      <c r="I81" s="5"/>
+      <c r="N81" s="2"/>
+    </row>
+    <row r="82" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A82" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B82" s="5">
+        <v>0</v>
+      </c>
+      <c r="C82" s="5">
+        <v>0</v>
+      </c>
       <c r="D82" s="5"/>
-      <c r="E82" s="5"/>
-      <c r="F82" s="5"/>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A83" s="9"/>
-      <c r="B83" s="9"/>
-      <c r="C83" s="5"/>
+      <c r="E82" s="5">
+        <v>0</v>
+      </c>
+      <c r="F82" s="5">
+        <v>0</v>
+      </c>
+      <c r="G82" s="5"/>
+      <c r="H82" s="5"/>
+      <c r="I82" s="5"/>
+    </row>
+    <row r="83" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A83" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B83" s="5">
+        <v>2</v>
+      </c>
+      <c r="C83" s="5">
+        <v>0</v>
+      </c>
       <c r="D83" s="5"/>
-      <c r="E83" s="5"/>
-      <c r="F83" s="5"/>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A84" s="9"/>
-      <c r="B84" s="9"/>
-      <c r="C84" s="5"/>
+      <c r="E83" s="5">
+        <v>2</v>
+      </c>
+      <c r="F83" s="5">
+        <v>2</v>
+      </c>
+      <c r="G83" s="5"/>
+      <c r="H83" s="5"/>
+      <c r="I83" s="5"/>
+      <c r="R83" s="1"/>
+    </row>
+    <row r="84" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A84" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B84" s="5">
+        <v>1</v>
+      </c>
+      <c r="C84" s="5">
+        <v>0</v>
+      </c>
       <c r="D84" s="5"/>
-      <c r="E84" s="5"/>
-      <c r="F84" s="5"/>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A85" s="9"/>
-      <c r="B85" s="9"/>
-      <c r="C85" s="5"/>
+      <c r="E84" s="5">
+        <v>1</v>
+      </c>
+      <c r="F84" s="5">
+        <v>1</v>
+      </c>
+      <c r="G84" s="5"/>
+      <c r="H84" s="5"/>
+      <c r="I84" s="5"/>
+      <c r="R84" s="1"/>
+    </row>
+    <row r="85" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A85" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B85" s="5">
+        <v>1</v>
+      </c>
+      <c r="C85" s="5">
+        <v>1</v>
+      </c>
       <c r="D85" s="5"/>
-      <c r="E85" s="5"/>
-      <c r="F85" s="5"/>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A86" s="9"/>
-      <c r="B86" s="9"/>
-      <c r="C86" s="5"/>
+      <c r="E85" s="5">
+        <v>1</v>
+      </c>
+      <c r="F85" s="5">
+        <v>1</v>
+      </c>
+      <c r="G85" s="5"/>
+      <c r="H85" s="5"/>
+      <c r="I85" s="5"/>
+      <c r="R85" s="1"/>
+    </row>
+    <row r="86" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A86" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B86" s="5">
+        <v>3</v>
+      </c>
+      <c r="C86" s="5">
+        <v>0</v>
+      </c>
       <c r="D86" s="5"/>
-      <c r="E86" s="5"/>
-      <c r="F86" s="5"/>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A87" s="9"/>
-      <c r="B87" s="9"/>
-      <c r="C87" s="5"/>
+      <c r="E86" s="5">
+        <v>2</v>
+      </c>
+      <c r="F86" s="5">
+        <v>2</v>
+      </c>
+      <c r="G86" s="5"/>
+      <c r="H86" s="5"/>
+      <c r="I86" s="5"/>
+      <c r="R86" s="2"/>
+    </row>
+    <row r="87" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A87" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B87" s="5">
+        <v>0</v>
+      </c>
+      <c r="C87" s="5">
+        <v>0</v>
+      </c>
       <c r="D87" s="5"/>
-      <c r="E87" s="5"/>
-      <c r="F87" s="5"/>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A88" s="9"/>
-      <c r="B88" s="9"/>
+      <c r="E87" s="5">
+        <v>0</v>
+      </c>
+      <c r="F87" s="5">
+        <v>0</v>
+      </c>
+      <c r="G87" s="5"/>
+      <c r="H87" s="5"/>
+      <c r="I87" s="5"/>
+      <c r="R87" s="2"/>
+    </row>
+    <row r="88" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A88" s="3">
+        <v>46256</v>
+      </c>
+      <c r="B88" s="5">
+        <v>9</v>
+      </c>
       <c r="C88" s="5"/>
       <c r="D88" s="5"/>
-      <c r="E88" s="5"/>
-      <c r="F88" s="5"/>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A89" s="9"/>
-      <c r="B89" s="9"/>
-      <c r="C89" s="5"/>
+      <c r="E88" s="5">
+        <v>0</v>
+      </c>
+      <c r="F88" s="5">
+        <v>6</v>
+      </c>
+      <c r="G88" s="5"/>
+      <c r="H88" s="5"/>
+      <c r="I88" s="5"/>
+      <c r="M88" s="1"/>
+      <c r="R88" s="2"/>
+    </row>
+    <row r="89" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A89" s="3">
+        <v>46257</v>
+      </c>
+      <c r="B89" s="5">
+        <v>0</v>
+      </c>
+      <c r="C89" s="5">
+        <v>0</v>
+      </c>
       <c r="D89" s="5"/>
-      <c r="E89" s="5"/>
-      <c r="F89" s="5"/>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A90" s="9"/>
-      <c r="B90" s="9"/>
-      <c r="C90" s="5"/>
+      <c r="E89" s="5">
+        <v>0</v>
+      </c>
+      <c r="F89" s="5">
+        <v>0</v>
+      </c>
+      <c r="G89" s="5"/>
+      <c r="H89" s="5"/>
+      <c r="I89" s="5"/>
+      <c r="M89" s="1"/>
+      <c r="R89" s="2"/>
+    </row>
+    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A90" s="3">
+        <v>46258</v>
+      </c>
+      <c r="B90" s="5">
+        <v>0</v>
+      </c>
+      <c r="C90" s="5">
+        <v>0</v>
+      </c>
       <c r="D90" s="5"/>
-      <c r="E90" s="5"/>
-      <c r="F90" s="5"/>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A91" s="9"/>
-      <c r="B91" s="9"/>
-      <c r="C91" s="5"/>
+      <c r="E90" s="5">
+        <v>1</v>
+      </c>
+      <c r="F90" s="5">
+        <v>0</v>
+      </c>
+      <c r="G90" s="5"/>
+      <c r="H90" s="5"/>
+      <c r="I90" s="5"/>
+      <c r="M90" s="1"/>
+      <c r="R90" s="2"/>
+    </row>
+    <row r="91" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A91" s="3">
+        <v>46259</v>
+      </c>
+      <c r="B91" s="5">
+        <v>1</v>
+      </c>
+      <c r="C91" s="5">
+        <v>1</v>
+      </c>
       <c r="D91" s="5"/>
-      <c r="E91" s="5"/>
-      <c r="F91" s="5"/>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A92" s="9"/>
-      <c r="B92" s="9"/>
-      <c r="C92" s="5"/>
+      <c r="E91" s="5">
+        <v>1</v>
+      </c>
+      <c r="F91" s="5">
+        <v>1</v>
+      </c>
+      <c r="G91" s="5"/>
+      <c r="H91" s="5"/>
+      <c r="I91" s="5"/>
+      <c r="M91" s="1"/>
+      <c r="R91" s="2"/>
+    </row>
+    <row r="92" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A92" s="3">
+        <v>46260</v>
+      </c>
+      <c r="B92" s="5">
+        <v>0</v>
+      </c>
+      <c r="C92" s="5">
+        <v>0</v>
+      </c>
       <c r="D92" s="5"/>
-      <c r="E92" s="5"/>
-      <c r="F92" s="5"/>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A93" s="9"/>
-      <c r="B93" s="9"/>
-      <c r="C93" s="5"/>
+      <c r="E92" s="5">
+        <v>0</v>
+      </c>
+      <c r="F92" s="5">
+        <v>0</v>
+      </c>
+      <c r="G92" s="5"/>
+      <c r="H92" s="5"/>
+      <c r="I92" s="5"/>
+      <c r="M92" s="1"/>
+      <c r="R92" s="2"/>
+    </row>
+    <row r="93" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A93" s="3">
+        <v>46261</v>
+      </c>
+      <c r="B93" s="5">
+        <v>1</v>
+      </c>
+      <c r="C93" s="5">
+        <v>1</v>
+      </c>
       <c r="D93" s="5"/>
-      <c r="E93" s="5"/>
-      <c r="F93" s="5"/>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A94" s="9"/>
-      <c r="B94" s="9"/>
-      <c r="C94" s="5"/>
+      <c r="E93" s="5">
+        <v>2</v>
+      </c>
+      <c r="F93" s="5">
+        <v>1</v>
+      </c>
+      <c r="G93" s="5"/>
+      <c r="H93" s="5"/>
+      <c r="I93" s="5"/>
+      <c r="M93" s="1"/>
+      <c r="R93" s="2"/>
+    </row>
+    <row r="94" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A94" s="3">
+        <v>46262</v>
+      </c>
+      <c r="B94" s="5">
+        <v>5</v>
+      </c>
+      <c r="C94" s="5">
+        <v>5</v>
+      </c>
       <c r="D94" s="5"/>
-      <c r="E94" s="5"/>
-      <c r="F94" s="5"/>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A95" s="9"/>
-      <c r="B95" s="9"/>
-      <c r="C95" s="5"/>
+      <c r="E94" s="5">
+        <v>0</v>
+      </c>
+      <c r="F94" s="5">
+        <v>5</v>
+      </c>
+      <c r="G94" s="5"/>
+      <c r="H94" s="5"/>
+      <c r="I94" s="5"/>
+      <c r="M94" s="1"/>
+      <c r="R94" s="2"/>
+    </row>
+    <row r="95" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A95" s="3">
+        <v>46263</v>
+      </c>
+      <c r="B95" s="5">
+        <v>6</v>
+      </c>
+      <c r="C95" s="5">
+        <v>6</v>
+      </c>
       <c r="D95" s="5"/>
-      <c r="E95" s="5"/>
-      <c r="F95" s="5"/>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A96" s="9"/>
-      <c r="B96" s="9"/>
-      <c r="C96" s="5"/>
+      <c r="E95" s="5">
+        <v>0</v>
+      </c>
+      <c r="F95" s="5">
+        <v>3</v>
+      </c>
+      <c r="G95" s="5"/>
+      <c r="H95" s="5"/>
+      <c r="I95" s="5"/>
+      <c r="M95" s="1"/>
+      <c r="R95" s="2"/>
+    </row>
+    <row r="96" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A96" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B96" s="5">
+        <v>8</v>
+      </c>
+      <c r="C96" s="5">
+        <v>4</v>
+      </c>
       <c r="D96" s="5"/>
-      <c r="E96" s="5"/>
-      <c r="F96" s="5"/>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A97" s="9"/>
-      <c r="B97" s="9"/>
-      <c r="C97" s="5"/>
+      <c r="E96" s="5">
+        <v>1</v>
+      </c>
+      <c r="F96" s="5">
+        <v>1</v>
+      </c>
+      <c r="G96" s="5"/>
+      <c r="H96" s="5"/>
+      <c r="I96" s="5"/>
+      <c r="M96" s="1"/>
+      <c r="R96" s="2"/>
+    </row>
+    <row r="97" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A97" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B97" s="5">
+        <v>3</v>
+      </c>
+      <c r="C97" s="5">
+        <v>1</v>
+      </c>
       <c r="D97" s="5"/>
-      <c r="E97" s="5"/>
-      <c r="F97" s="5"/>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A98" s="9"/>
-      <c r="B98" s="9"/>
-      <c r="C98" s="5"/>
+      <c r="E97" s="5">
+        <v>2</v>
+      </c>
+      <c r="F97" s="5">
+        <v>2</v>
+      </c>
+      <c r="G97" s="5"/>
+      <c r="H97" s="5"/>
+      <c r="I97" s="5"/>
+      <c r="J97" s="1"/>
+      <c r="M97" s="1"/>
+    </row>
+    <row r="98" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A98" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B98" s="5">
+        <v>2</v>
+      </c>
+      <c r="C98" s="5">
+        <v>2</v>
+      </c>
       <c r="D98" s="5"/>
-      <c r="E98" s="5"/>
-      <c r="F98" s="5"/>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A99" s="9"/>
-      <c r="B99" s="9"/>
-      <c r="C99" s="5"/>
+      <c r="E98" s="5">
+        <v>5</v>
+      </c>
+      <c r="F98" s="5">
+        <v>3</v>
+      </c>
+      <c r="G98" s="5"/>
+      <c r="H98" s="5"/>
+      <c r="I98" s="5"/>
+      <c r="J98" s="1"/>
+      <c r="M98" s="1"/>
+    </row>
+    <row r="99" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A99" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B99" s="5">
+        <v>0</v>
+      </c>
+      <c r="C99" s="5">
+        <v>0</v>
+      </c>
       <c r="D99" s="5"/>
-      <c r="E99" s="5"/>
-      <c r="F99" s="5"/>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A100" s="9"/>
-      <c r="B100" s="9"/>
-      <c r="C100" s="5"/>
+      <c r="E99" s="5">
+        <v>5</v>
+      </c>
+      <c r="F99" s="5">
+        <v>2</v>
+      </c>
+      <c r="G99" s="5"/>
+      <c r="H99" s="5"/>
+      <c r="I99" s="5"/>
+      <c r="J99" s="2"/>
+      <c r="M99" s="1"/>
+    </row>
+    <row r="100" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A100" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B100" s="5">
+        <v>0</v>
+      </c>
+      <c r="C100" s="5">
+        <v>0</v>
+      </c>
       <c r="D100" s="5"/>
-      <c r="E100" s="5"/>
-      <c r="F100" s="5"/>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A101" s="9"/>
-      <c r="B101" s="9"/>
-      <c r="C101" s="5"/>
+      <c r="E100" s="5">
+        <v>0</v>
+      </c>
+      <c r="F100" s="5">
+        <v>0</v>
+      </c>
+      <c r="G100" s="5"/>
+      <c r="H100" s="5">
+        <v>1</v>
+      </c>
+      <c r="I100" s="5">
+        <v>1</v>
+      </c>
+      <c r="J100" s="2"/>
+      <c r="M100" s="1"/>
+    </row>
+    <row r="101" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A101" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B101" s="5">
+        <v>3</v>
+      </c>
+      <c r="C101" s="5">
+        <v>3</v>
+      </c>
       <c r="D101" s="5"/>
-      <c r="E101" s="5"/>
-      <c r="F101" s="5"/>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A102" s="9"/>
-      <c r="B102" s="9"/>
-      <c r="C102" s="5"/>
+      <c r="E101" s="5">
+        <v>3</v>
+      </c>
+      <c r="F101" s="5">
+        <v>2</v>
+      </c>
+      <c r="G101" s="5"/>
+      <c r="H101" s="5">
+        <v>1</v>
+      </c>
+      <c r="I101" s="5">
+        <v>1</v>
+      </c>
+      <c r="J101" s="2"/>
+      <c r="M101" s="1"/>
+    </row>
+    <row r="102" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A102" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B102" s="5">
+        <v>1</v>
+      </c>
+      <c r="C102" s="5">
+        <v>1</v>
+      </c>
       <c r="D102" s="5"/>
-      <c r="E102" s="5"/>
-      <c r="F102" s="5"/>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A103" s="9"/>
-      <c r="B103" s="9"/>
-      <c r="C103" s="5"/>
+      <c r="E102" s="5">
+        <v>1</v>
+      </c>
+      <c r="F102" s="5">
+        <v>1</v>
+      </c>
+      <c r="G102" s="5"/>
+      <c r="H102" s="5">
+        <v>0</v>
+      </c>
+      <c r="I102" s="5">
+        <v>0</v>
+      </c>
+      <c r="J102" s="2"/>
+    </row>
+    <row r="103" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A103" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B103" s="5">
+        <v>3</v>
+      </c>
+      <c r="C103" s="5">
+        <v>3</v>
+      </c>
       <c r="D103" s="5"/>
-      <c r="E103" s="5"/>
-      <c r="F103" s="5"/>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A104" s="9"/>
-      <c r="B104" s="9"/>
-      <c r="C104" s="5"/>
+      <c r="E103" s="5">
+        <v>1</v>
+      </c>
+      <c r="F103" s="5">
+        <v>1</v>
+      </c>
+      <c r="G103" s="5"/>
+      <c r="H103" s="5">
+        <v>0</v>
+      </c>
+      <c r="I103" s="5">
+        <v>0</v>
+      </c>
+      <c r="J103" s="2"/>
+    </row>
+    <row r="104" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A104" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B104" s="5">
+        <v>0</v>
+      </c>
+      <c r="C104" s="5">
+        <v>0</v>
+      </c>
       <c r="D104" s="5"/>
-      <c r="E104" s="5"/>
-      <c r="F104" s="5"/>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A105" s="9"/>
-      <c r="B105" s="9"/>
-      <c r="C105" s="5"/>
+      <c r="E104" s="5">
+        <v>15</v>
+      </c>
+      <c r="F104" s="5">
+        <v>7</v>
+      </c>
+      <c r="G104" s="5"/>
+      <c r="H104" s="5">
+        <v>6</v>
+      </c>
+      <c r="I104" s="5">
+        <v>4</v>
+      </c>
+      <c r="J104" s="2"/>
+    </row>
+    <row r="105" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A105" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B105" s="5">
+        <v>0</v>
+      </c>
+      <c r="C105" s="5">
+        <v>0</v>
+      </c>
       <c r="D105" s="5"/>
-      <c r="E105" s="5"/>
-      <c r="F105" s="5"/>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A106" s="9"/>
-      <c r="B106" s="9"/>
-      <c r="C106" s="5"/>
+      <c r="E105" s="5">
+        <v>3</v>
+      </c>
+      <c r="F105" s="5">
+        <v>3</v>
+      </c>
+      <c r="G105" s="5"/>
+      <c r="H105" s="5">
+        <v>0</v>
+      </c>
+      <c r="I105" s="5">
+        <v>0</v>
+      </c>
+      <c r="J105" s="2"/>
+    </row>
+    <row r="106" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A106" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B106" s="5">
+        <v>21</v>
+      </c>
+      <c r="C106" s="5">
+        <v>10</v>
+      </c>
       <c r="D106" s="5"/>
-      <c r="E106" s="5"/>
-      <c r="F106" s="5"/>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A107" s="9"/>
-      <c r="B107" s="9"/>
-      <c r="C107" s="5"/>
+      <c r="E106" s="5">
+        <v>6</v>
+      </c>
+      <c r="F106" s="5">
+        <v>2</v>
+      </c>
+      <c r="G106" s="5"/>
+      <c r="H106" s="5">
+        <v>0</v>
+      </c>
+      <c r="I106" s="5">
+        <v>0</v>
+      </c>
+      <c r="J106" s="2"/>
+    </row>
+    <row r="107" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A107" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B107" s="5">
+        <v>1</v>
+      </c>
+      <c r="C107" s="5">
+        <v>1</v>
+      </c>
       <c r="D107" s="5"/>
-      <c r="E107" s="5"/>
-      <c r="F107" s="5"/>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A108" s="9"/>
-      <c r="B108" s="9"/>
-      <c r="C108" s="5"/>
+      <c r="E107" s="5">
+        <v>2</v>
+      </c>
+      <c r="F107" s="5">
+        <v>2</v>
+      </c>
+      <c r="G107" s="5"/>
+      <c r="H107" s="5">
+        <v>1</v>
+      </c>
+      <c r="I107" s="5">
+        <v>1</v>
+      </c>
+      <c r="J107" s="2"/>
+    </row>
+    <row r="108" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A108" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B108" s="5">
+        <v>0</v>
+      </c>
+      <c r="C108" s="5">
+        <v>0</v>
+      </c>
       <c r="D108" s="5"/>
-      <c r="E108" s="5"/>
-      <c r="F108" s="5"/>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A109" s="9"/>
-      <c r="B109" s="9"/>
-      <c r="C109" s="5"/>
+      <c r="E108" s="5">
+        <v>11</v>
+      </c>
+      <c r="F108" s="5">
+        <v>7</v>
+      </c>
+      <c r="G108" s="5"/>
+      <c r="H108" s="5">
+        <v>0</v>
+      </c>
+      <c r="I108" s="5">
+        <v>0</v>
+      </c>
+      <c r="J108" s="2"/>
+      <c r="K108" t="s">
+        <v>73</v>
+      </c>
+      <c r="N108" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="109" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A109" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B109" s="5">
+        <v>2</v>
+      </c>
+      <c r="C109" s="5">
+        <v>2</v>
+      </c>
       <c r="D109" s="5"/>
-      <c r="E109" s="5"/>
-      <c r="F109" s="5"/>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A110" s="9"/>
-      <c r="B110" s="9"/>
-      <c r="C110" s="5"/>
+      <c r="E109" s="5">
+        <v>0</v>
+      </c>
+      <c r="F109" s="5">
+        <v>0</v>
+      </c>
+      <c r="G109" s="5"/>
+      <c r="H109" s="5">
+        <v>0</v>
+      </c>
+      <c r="I109" s="5">
+        <v>0</v>
+      </c>
+      <c r="K109" t="s">
+        <v>2</v>
+      </c>
+      <c r="L109" t="s">
+        <v>3</v>
+      </c>
+      <c r="N109" t="s">
+        <v>2</v>
+      </c>
+      <c r="O109" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q109" t="s">
+        <v>2</v>
+      </c>
+      <c r="R109" t="s">
+        <v>3</v>
+      </c>
+      <c r="T109" t="s">
+        <v>2</v>
+      </c>
+      <c r="U109" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="110" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A110" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B110" s="5">
+        <v>1</v>
+      </c>
+      <c r="C110" s="5">
+        <v>1</v>
+      </c>
       <c r="D110" s="5"/>
-      <c r="E110" s="5"/>
-      <c r="F110" s="5"/>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A111" s="9"/>
-      <c r="B111" s="9"/>
-      <c r="C111" s="5"/>
+      <c r="E110" s="5">
+        <v>15</v>
+      </c>
+      <c r="F110" s="5">
+        <v>9</v>
+      </c>
+      <c r="G110" s="5"/>
+      <c r="H110" s="5">
+        <v>0</v>
+      </c>
+      <c r="I110" s="5">
+        <v>0</v>
+      </c>
+      <c r="K110" s="2"/>
+      <c r="N110" s="2"/>
+      <c r="Q110" s="2"/>
+      <c r="T110" s="2"/>
+    </row>
+    <row r="111" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A111" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B111" s="5">
+        <v>0</v>
+      </c>
+      <c r="C111" s="5">
+        <v>0</v>
+      </c>
       <c r="D111" s="5"/>
-      <c r="E111" s="5"/>
-      <c r="F111" s="5"/>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A112" s="9"/>
-      <c r="B112" s="9"/>
-      <c r="C112" s="5"/>
+      <c r="E111" s="5">
+        <v>2</v>
+      </c>
+      <c r="F111" s="5">
+        <v>2</v>
+      </c>
+      <c r="G111" s="5"/>
+      <c r="H111" s="5">
+        <v>0</v>
+      </c>
+      <c r="I111" s="5">
+        <v>0</v>
+      </c>
+      <c r="K111" s="1">
+        <v>41518</v>
+      </c>
+      <c r="L111">
+        <v>0</v>
+      </c>
+      <c r="N111" s="1">
+        <v>41518</v>
+      </c>
+      <c r="O111">
+        <v>0</v>
+      </c>
+      <c r="Q111" s="1">
+        <v>41518</v>
+      </c>
+      <c r="R111">
+        <v>15</v>
+      </c>
+      <c r="T111" s="1">
+        <v>41518</v>
+      </c>
+      <c r="U111">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="112" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A112" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B112" s="5">
+        <v>0</v>
+      </c>
+      <c r="C112" s="5">
+        <v>0</v>
+      </c>
       <c r="D112" s="5"/>
-      <c r="E112" s="5"/>
-      <c r="F112" s="5"/>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A113" s="9"/>
-      <c r="B113" s="9"/>
-      <c r="C113" s="5"/>
+      <c r="E112" s="5">
+        <v>1</v>
+      </c>
+      <c r="F112" s="5">
+        <v>1</v>
+      </c>
+      <c r="G112" s="5"/>
+      <c r="H112" s="5">
+        <v>1</v>
+      </c>
+      <c r="I112" s="5">
+        <v>1</v>
+      </c>
+      <c r="K112" s="1">
+        <v>41883</v>
+      </c>
+      <c r="L112">
+        <v>0</v>
+      </c>
+      <c r="N112" s="1">
+        <v>41883</v>
+      </c>
+      <c r="O112">
+        <v>0</v>
+      </c>
+      <c r="Q112" s="1">
+        <v>41883</v>
+      </c>
+      <c r="R112">
+        <v>2</v>
+      </c>
+      <c r="T112" s="1">
+        <v>41883</v>
+      </c>
+      <c r="U112">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="113" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A113" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B113" s="5">
+        <v>0</v>
+      </c>
+      <c r="C113" s="5">
+        <v>0</v>
+      </c>
       <c r="D113" s="5"/>
-      <c r="E113" s="5"/>
-      <c r="F113" s="5"/>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A114" s="9"/>
-      <c r="B114" s="9"/>
+      <c r="E113" s="5">
+        <v>3</v>
+      </c>
+      <c r="F113" s="5">
+        <v>3</v>
+      </c>
+      <c r="G113" s="5"/>
+      <c r="H113" s="5">
+        <v>0</v>
+      </c>
+      <c r="I113" s="5">
+        <v>0</v>
+      </c>
+      <c r="K113" s="1">
+        <v>42248</v>
+      </c>
+      <c r="L113">
+        <v>1</v>
+      </c>
+      <c r="N113" s="1">
+        <v>42248</v>
+      </c>
+      <c r="O113">
+        <v>1</v>
+      </c>
+      <c r="Q113" s="1">
+        <v>42248</v>
+      </c>
+      <c r="R113">
+        <v>1</v>
+      </c>
+      <c r="T113" s="1">
+        <v>42248</v>
+      </c>
+      <c r="U113">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A114" s="3"/>
       <c r="C114" s="5"/>
       <c r="D114" s="5"/>
       <c r="E114" s="5"/>
-      <c r="F114" s="5"/>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A115" s="9"/>
-      <c r="B115" s="9"/>
+      <c r="K114" s="1">
+        <v>42614</v>
+      </c>
+      <c r="L114">
+        <v>0</v>
+      </c>
+      <c r="N114" s="1">
+        <v>42614</v>
+      </c>
+      <c r="O114">
+        <v>0</v>
+      </c>
+      <c r="Q114" s="1">
+        <v>42614</v>
+      </c>
+      <c r="R114">
+        <v>3</v>
+      </c>
+      <c r="T114" s="1">
+        <v>42614</v>
+      </c>
+      <c r="U114">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="115" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A115" s="3"/>
       <c r="C115" s="5"/>
       <c r="D115" s="5"/>
       <c r="E115" s="5"/>
-      <c r="F115" s="5"/>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A116" s="9"/>
-      <c r="B116" s="9"/>
+      <c r="K115" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="L115" s="14"/>
+      <c r="M115" s="14"/>
+      <c r="N115" s="2"/>
+      <c r="Q115" s="2"/>
+      <c r="T115" s="2"/>
+    </row>
+    <row r="116" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A116" s="3"/>
       <c r="C116" s="5"/>
       <c r="D116" s="5"/>
       <c r="E116" s="5"/>
-      <c r="F116" s="5"/>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A117" s="9"/>
-      <c r="B117" s="9"/>
+      <c r="K116" t="s">
+        <v>71</v>
+      </c>
+      <c r="N116" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q116" s="2"/>
+      <c r="T116" s="2"/>
+    </row>
+    <row r="117" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A117" s="3"/>
       <c r="C117" s="5"/>
       <c r="D117" s="5"/>
       <c r="E117" s="5"/>
-      <c r="F117" s="5"/>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A118" s="9"/>
-      <c r="B118" s="9"/>
+      <c r="K117" t="s">
+        <v>2</v>
+      </c>
+      <c r="L117" t="s">
+        <v>3</v>
+      </c>
+      <c r="N117" t="s">
+        <v>2</v>
+      </c>
+      <c r="O117" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q117" s="2"/>
+      <c r="T117" s="2"/>
+    </row>
+    <row r="118" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A118" s="3"/>
       <c r="C118" s="5"/>
       <c r="D118" s="5"/>
       <c r="E118" s="5"/>
-      <c r="F118" s="5"/>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A119" s="9"/>
-      <c r="B119" s="9"/>
+      <c r="K118" s="1">
+        <v>41518</v>
+      </c>
+      <c r="L118">
+        <v>1</v>
+      </c>
+      <c r="N118" s="1">
+        <v>41518</v>
+      </c>
+      <c r="O118">
+        <v>1</v>
+      </c>
+      <c r="Q118" s="2"/>
+      <c r="T118" s="2"/>
+    </row>
+    <row r="119" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A119" s="2"/>
       <c r="C119" s="5"/>
       <c r="D119" s="5"/>
       <c r="E119" s="5"/>
-      <c r="F119" s="5"/>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A120" s="9"/>
-      <c r="B120" s="9"/>
+      <c r="K119" s="1">
+        <v>41883</v>
+      </c>
+      <c r="L119">
+        <v>0</v>
+      </c>
+      <c r="N119" s="1">
+        <v>41883</v>
+      </c>
+      <c r="O119">
+        <v>0</v>
+      </c>
+      <c r="Q119" s="2"/>
+      <c r="T119" s="2"/>
+    </row>
+    <row r="120" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A120" s="2"/>
       <c r="C120" s="5"/>
       <c r="D120" s="5"/>
       <c r="E120" s="5"/>
-      <c r="F120" s="5"/>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A121" s="9"/>
-      <c r="B121" s="9"/>
+      <c r="K120" s="1">
+        <v>42248</v>
+      </c>
+      <c r="L120">
+        <v>0</v>
+      </c>
+      <c r="N120" s="1">
+        <v>42248</v>
+      </c>
+      <c r="O120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A121" s="2"/>
       <c r="C121" s="5"/>
       <c r="D121" s="5"/>
       <c r="E121" s="5"/>
-      <c r="F121" s="5"/>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A122" s="9"/>
-      <c r="B122" s="9"/>
+      <c r="K121" s="1">
+        <v>42614</v>
+      </c>
+      <c r="L121">
+        <v>0</v>
+      </c>
+      <c r="N121" s="1">
+        <v>42614</v>
+      </c>
+      <c r="O121">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A122" s="2"/>
       <c r="C122" s="5"/>
       <c r="D122" s="5"/>
       <c r="E122" s="5"/>
-      <c r="F122" s="5"/>
-    </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A123" s="9"/>
-      <c r="B123" s="9"/>
+    </row>
+    <row r="123" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A123" s="2"/>
       <c r="C123" s="5"/>
       <c r="D123" s="5"/>
       <c r="E123" s="5"/>
-      <c r="F123" s="5"/>
-    </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="9"/>
       <c r="B124" s="9"/>
       <c r="C124" s="5"/>
       <c r="D124" s="5"/>
       <c r="E124" s="5"/>
       <c r="F124" s="5"/>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J124" s="2"/>
+    </row>
+    <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="9"/>
       <c r="B125" s="9"/>
       <c r="C125" s="5"/>
@@ -3362,7 +4128,7 @@
       <c r="E125" s="5"/>
       <c r="F125" s="5"/>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="9"/>
       <c r="B126" s="9"/>
       <c r="C126" s="5"/>
@@ -3370,7 +4136,7 @@
       <c r="E126" s="5"/>
       <c r="F126" s="5"/>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="9"/>
       <c r="B127" s="9"/>
       <c r="C127" s="5"/>
@@ -3378,7 +4144,7 @@
       <c r="E127" s="5"/>
       <c r="F127" s="5"/>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="9"/>
       <c r="B128" s="9"/>
       <c r="C128" s="5"/>
@@ -4132,336 +4898,660 @@
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" s="11"/>
-      <c r="B222" s="11"/>
+      <c r="B222" s="9"/>
+      <c r="C222" s="5"/>
+      <c r="D222" s="5"/>
+      <c r="E222" s="5"/>
+      <c r="F222" s="5"/>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" s="11"/>
-      <c r="B223" s="11"/>
+      <c r="B223" s="9"/>
+      <c r="C223" s="5"/>
+      <c r="D223" s="5"/>
+      <c r="E223" s="5"/>
+      <c r="F223" s="5"/>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" s="11"/>
-      <c r="B224" s="11"/>
-    </row>
-    <row r="225" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B224" s="9"/>
+      <c r="C224" s="5"/>
+      <c r="D224" s="5"/>
+      <c r="E224" s="5"/>
+      <c r="F224" s="5"/>
+    </row>
+    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" s="11"/>
-      <c r="B225" s="11"/>
-    </row>
-    <row r="226" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B225" s="9"/>
+      <c r="C225" s="5"/>
+      <c r="D225" s="5"/>
+      <c r="E225" s="5"/>
+      <c r="F225" s="5"/>
+    </row>
+    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" s="11"/>
-      <c r="B226" s="11"/>
-    </row>
-    <row r="227" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B226" s="9"/>
+      <c r="C226" s="5"/>
+      <c r="D226" s="5"/>
+      <c r="E226" s="5"/>
+      <c r="F226" s="5"/>
+    </row>
+    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" s="11"/>
-      <c r="B227" s="11"/>
-    </row>
-    <row r="228" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B227" s="9"/>
+      <c r="C227" s="5"/>
+      <c r="D227" s="5"/>
+      <c r="E227" s="5"/>
+      <c r="F227" s="5"/>
+    </row>
+    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" s="11"/>
-      <c r="B228" s="11"/>
-    </row>
-    <row r="229" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B228" s="9"/>
+      <c r="C228" s="5"/>
+      <c r="D228" s="5"/>
+      <c r="E228" s="5"/>
+      <c r="F228" s="5"/>
+    </row>
+    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" s="11"/>
-      <c r="B229" s="11"/>
-    </row>
-    <row r="230" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B229" s="9"/>
+      <c r="C229" s="5"/>
+      <c r="D229" s="5"/>
+      <c r="E229" s="5"/>
+      <c r="F229" s="5"/>
+    </row>
+    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" s="11"/>
-      <c r="B230" s="11"/>
-    </row>
-    <row r="231" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B230" s="9"/>
+      <c r="C230" s="5"/>
+      <c r="D230" s="5"/>
+      <c r="E230" s="5"/>
+      <c r="F230" s="5"/>
+    </row>
+    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" s="11"/>
-      <c r="B231" s="11"/>
-    </row>
-    <row r="232" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B231" s="9"/>
+      <c r="C231" s="5"/>
+      <c r="D231" s="5"/>
+      <c r="E231" s="5"/>
+      <c r="F231" s="5"/>
+    </row>
+    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" s="11"/>
-      <c r="B232" s="11"/>
-    </row>
-    <row r="233" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B232" s="9"/>
+      <c r="C232" s="5"/>
+      <c r="D232" s="5"/>
+      <c r="E232" s="5"/>
+      <c r="F232" s="5"/>
+    </row>
+    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" s="11"/>
-      <c r="B233" s="11"/>
-    </row>
-    <row r="234" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B233" s="9"/>
+      <c r="C233" s="5"/>
+      <c r="D233" s="5"/>
+      <c r="E233" s="5"/>
+      <c r="F233" s="5"/>
+    </row>
+    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" s="11"/>
-      <c r="B234" s="11"/>
-    </row>
-    <row r="235" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B234" s="9"/>
+      <c r="C234" s="5"/>
+      <c r="D234" s="5"/>
+      <c r="E234" s="5"/>
+      <c r="F234" s="5"/>
+    </row>
+    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" s="11"/>
-      <c r="B235" s="11"/>
-    </row>
-    <row r="236" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B235" s="9"/>
+      <c r="C235" s="5"/>
+      <c r="D235" s="5"/>
+      <c r="E235" s="5"/>
+      <c r="F235" s="5"/>
+    </row>
+    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" s="11"/>
-      <c r="B236" s="11"/>
-    </row>
-    <row r="237" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B236" s="9"/>
+      <c r="C236" s="5"/>
+      <c r="D236" s="5"/>
+      <c r="E236" s="5"/>
+      <c r="F236" s="5"/>
+    </row>
+    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" s="11"/>
-      <c r="B237" s="11"/>
-    </row>
-    <row r="238" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B237" s="9"/>
+      <c r="C237" s="5"/>
+      <c r="D237" s="5"/>
+      <c r="E237" s="5"/>
+      <c r="F237" s="5"/>
+    </row>
+    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" s="11"/>
-      <c r="B238" s="11"/>
-    </row>
-    <row r="239" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B238" s="9"/>
+      <c r="C238" s="5"/>
+      <c r="D238" s="5"/>
+      <c r="E238" s="5"/>
+      <c r="F238" s="5"/>
+    </row>
+    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" s="11"/>
-      <c r="B239" s="11"/>
-    </row>
-    <row r="240" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B239" s="9"/>
+      <c r="C239" s="5"/>
+      <c r="D239" s="5"/>
+      <c r="E239" s="5"/>
+      <c r="F239" s="5"/>
+    </row>
+    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" s="11"/>
-      <c r="B240" s="11"/>
-    </row>
-    <row r="241" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B240" s="9"/>
+      <c r="C240" s="5"/>
+      <c r="D240" s="5"/>
+      <c r="E240" s="5"/>
+      <c r="F240" s="5"/>
+    </row>
+    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" s="11"/>
-      <c r="B241" s="11"/>
-    </row>
-    <row r="242" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B241" s="9"/>
+      <c r="C241" s="5"/>
+      <c r="D241" s="5"/>
+      <c r="E241" s="5"/>
+      <c r="F241" s="5"/>
+    </row>
+    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" s="11"/>
-      <c r="B242" s="11"/>
-    </row>
-    <row r="243" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B242" s="9"/>
+      <c r="C242" s="5"/>
+      <c r="D242" s="5"/>
+      <c r="E242" s="5"/>
+      <c r="F242" s="5"/>
+    </row>
+    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" s="11"/>
-      <c r="B243" s="11"/>
-    </row>
-    <row r="244" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B243" s="9"/>
+      <c r="C243" s="5"/>
+      <c r="D243" s="5"/>
+      <c r="E243" s="5"/>
+      <c r="F243" s="5"/>
+    </row>
+    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" s="11"/>
-      <c r="B244" s="11"/>
-    </row>
-    <row r="245" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B244" s="9"/>
+      <c r="C244" s="5"/>
+      <c r="D244" s="5"/>
+      <c r="E244" s="5"/>
+      <c r="F244" s="5"/>
+    </row>
+    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" s="11"/>
-      <c r="B245" s="11"/>
-    </row>
-    <row r="246" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B245" s="9"/>
+      <c r="C245" s="5"/>
+      <c r="D245" s="5"/>
+      <c r="E245" s="5"/>
+      <c r="F245" s="5"/>
+    </row>
+    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" s="11"/>
-      <c r="B246" s="11"/>
-    </row>
-    <row r="247" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B246" s="9"/>
+      <c r="C246" s="5"/>
+      <c r="D246" s="5"/>
+      <c r="E246" s="5"/>
+      <c r="F246" s="5"/>
+    </row>
+    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" s="11"/>
-      <c r="B247" s="11"/>
-    </row>
-    <row r="248" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B247" s="9"/>
+      <c r="C247" s="5"/>
+      <c r="D247" s="5"/>
+      <c r="E247" s="5"/>
+      <c r="F247" s="5"/>
+    </row>
+    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" s="11"/>
-      <c r="B248" s="11"/>
-    </row>
-    <row r="249" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B248" s="9"/>
+      <c r="C248" s="5"/>
+      <c r="D248" s="5"/>
+      <c r="E248" s="5"/>
+      <c r="F248" s="5"/>
+    </row>
+    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" s="11"/>
-      <c r="B249" s="11"/>
-    </row>
-    <row r="250" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B249" s="9"/>
+      <c r="C249" s="5"/>
+      <c r="D249" s="5"/>
+      <c r="E249" s="5"/>
+      <c r="F249" s="5"/>
+    </row>
+    <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" s="11"/>
-      <c r="B250" s="11"/>
-    </row>
-    <row r="251" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B250" s="9"/>
+      <c r="C250" s="5"/>
+      <c r="D250" s="5"/>
+      <c r="E250" s="5"/>
+      <c r="F250" s="5"/>
+    </row>
+    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" s="11"/>
-      <c r="B251" s="11"/>
-    </row>
-    <row r="252" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B251" s="9"/>
+      <c r="C251" s="5"/>
+      <c r="D251" s="5"/>
+      <c r="E251" s="5"/>
+      <c r="F251" s="5"/>
+    </row>
+    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" s="11"/>
-      <c r="B252" s="11"/>
-    </row>
-    <row r="253" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B252" s="9"/>
+      <c r="C252" s="5"/>
+      <c r="D252" s="5"/>
+      <c r="E252" s="5"/>
+      <c r="F252" s="5"/>
+    </row>
+    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" s="11"/>
-      <c r="B253" s="11"/>
-    </row>
-    <row r="254" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B253" s="9"/>
+      <c r="C253" s="5"/>
+      <c r="D253" s="5"/>
+      <c r="E253" s="5"/>
+      <c r="F253" s="5"/>
+    </row>
+    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" s="11"/>
-      <c r="B254" s="11"/>
-    </row>
-    <row r="255" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B254" s="9"/>
+      <c r="C254" s="5"/>
+      <c r="D254" s="5"/>
+      <c r="E254" s="5"/>
+      <c r="F254" s="5"/>
+    </row>
+    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" s="11"/>
-      <c r="B255" s="11"/>
-    </row>
-    <row r="256" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B255" s="9"/>
+      <c r="C255" s="5"/>
+      <c r="D255" s="5"/>
+      <c r="E255" s="5"/>
+      <c r="F255" s="5"/>
+    </row>
+    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" s="11"/>
-      <c r="B256" s="11"/>
-    </row>
-    <row r="257" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B256" s="9"/>
+      <c r="C256" s="5"/>
+      <c r="D256" s="5"/>
+      <c r="E256" s="5"/>
+      <c r="F256" s="5"/>
+    </row>
+    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" s="11"/>
-      <c r="B257" s="11"/>
-    </row>
-    <row r="258" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B257" s="9"/>
+      <c r="C257" s="5"/>
+      <c r="D257" s="5"/>
+      <c r="E257" s="5"/>
+      <c r="F257" s="5"/>
+    </row>
+    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" s="11"/>
-      <c r="B258" s="11"/>
-    </row>
-    <row r="259" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B258" s="9"/>
+      <c r="C258" s="5"/>
+      <c r="D258" s="5"/>
+      <c r="E258" s="5"/>
+      <c r="F258" s="5"/>
+    </row>
+    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" s="11"/>
-      <c r="B259" s="11"/>
-    </row>
-    <row r="260" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B259" s="9"/>
+      <c r="C259" s="5"/>
+      <c r="D259" s="5"/>
+      <c r="E259" s="5"/>
+      <c r="F259" s="5"/>
+    </row>
+    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" s="11"/>
-      <c r="B260" s="11"/>
-    </row>
-    <row r="261" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B260" s="9"/>
+      <c r="C260" s="5"/>
+      <c r="D260" s="5"/>
+      <c r="E260" s="5"/>
+      <c r="F260" s="5"/>
+    </row>
+    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" s="11"/>
-      <c r="B261" s="11"/>
-    </row>
-    <row r="262" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B261" s="9"/>
+      <c r="C261" s="5"/>
+      <c r="D261" s="5"/>
+      <c r="E261" s="5"/>
+      <c r="F261" s="5"/>
+    </row>
+    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" s="11"/>
-      <c r="B262" s="11"/>
-    </row>
-    <row r="263" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B262" s="9"/>
+      <c r="C262" s="5"/>
+      <c r="D262" s="5"/>
+      <c r="E262" s="5"/>
+      <c r="F262" s="5"/>
+    </row>
+    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" s="11"/>
-      <c r="B263" s="11"/>
-    </row>
-    <row r="264" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B263" s="9"/>
+      <c r="C263" s="5"/>
+      <c r="D263" s="5"/>
+      <c r="E263" s="5"/>
+      <c r="F263" s="5"/>
+    </row>
+    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" s="11"/>
-      <c r="B264" s="11"/>
-    </row>
-    <row r="265" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B264" s="9"/>
+      <c r="C264" s="5"/>
+      <c r="D264" s="5"/>
+      <c r="E264" s="5"/>
+      <c r="F264" s="5"/>
+    </row>
+    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" s="11"/>
-      <c r="B265" s="11"/>
-    </row>
-    <row r="266" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B265" s="9"/>
+      <c r="C265" s="5"/>
+      <c r="D265" s="5"/>
+      <c r="E265" s="5"/>
+      <c r="F265" s="5"/>
+    </row>
+    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266" s="11"/>
-      <c r="B266" s="11"/>
-    </row>
-    <row r="267" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B266" s="9"/>
+      <c r="C266" s="5"/>
+      <c r="D266" s="5"/>
+      <c r="E266" s="5"/>
+      <c r="F266" s="5"/>
+    </row>
+    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267" s="11"/>
-      <c r="B267" s="11"/>
-    </row>
-    <row r="268" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B267" s="9"/>
+      <c r="C267" s="5"/>
+      <c r="D267" s="5"/>
+      <c r="E267" s="5"/>
+      <c r="F267" s="5"/>
+    </row>
+    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" s="11"/>
-      <c r="B268" s="11"/>
-    </row>
-    <row r="269" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B268" s="9"/>
+      <c r="C268" s="5"/>
+      <c r="D268" s="5"/>
+      <c r="E268" s="5"/>
+      <c r="F268" s="5"/>
+    </row>
+    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" s="11"/>
-      <c r="B269" s="11"/>
-    </row>
-    <row r="270" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B269" s="9"/>
+      <c r="C269" s="5"/>
+      <c r="D269" s="5"/>
+      <c r="E269" s="5"/>
+      <c r="F269" s="5"/>
+    </row>
+    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" s="11"/>
-      <c r="B270" s="11"/>
-    </row>
-    <row r="271" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B270" s="9"/>
+      <c r="C270" s="5"/>
+      <c r="D270" s="5"/>
+      <c r="E270" s="5"/>
+      <c r="F270" s="5"/>
+    </row>
+    <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" s="11"/>
-      <c r="B271" s="11"/>
-    </row>
-    <row r="272" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B271" s="9"/>
+      <c r="C271" s="5"/>
+      <c r="D271" s="5"/>
+      <c r="E271" s="5"/>
+      <c r="F271" s="5"/>
+    </row>
+    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" s="11"/>
-      <c r="B272" s="11"/>
-    </row>
-    <row r="273" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B272" s="9"/>
+      <c r="C272" s="5"/>
+      <c r="D272" s="5"/>
+      <c r="E272" s="5"/>
+      <c r="F272" s="5"/>
+    </row>
+    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" s="11"/>
-      <c r="B273" s="11"/>
-    </row>
-    <row r="274" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B273" s="9"/>
+      <c r="C273" s="5"/>
+      <c r="D273" s="5"/>
+      <c r="E273" s="5"/>
+      <c r="F273" s="5"/>
+    </row>
+    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" s="11"/>
-      <c r="B274" s="11"/>
-    </row>
-    <row r="275" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B274" s="9"/>
+      <c r="C274" s="5"/>
+      <c r="D274" s="5"/>
+      <c r="E274" s="5"/>
+      <c r="F274" s="5"/>
+    </row>
+    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" s="11"/>
-      <c r="B275" s="11"/>
-    </row>
-    <row r="276" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B275" s="9"/>
+      <c r="C275" s="5"/>
+      <c r="D275" s="5"/>
+      <c r="E275" s="5"/>
+      <c r="F275" s="5"/>
+    </row>
+    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" s="11"/>
-      <c r="B276" s="11"/>
-    </row>
-    <row r="277" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B276" s="9"/>
+      <c r="C276" s="5"/>
+      <c r="D276" s="5"/>
+      <c r="E276" s="5"/>
+      <c r="F276" s="5"/>
+    </row>
+    <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" s="11"/>
-      <c r="B277" s="11"/>
-    </row>
-    <row r="278" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B277" s="9"/>
+      <c r="C277" s="5"/>
+      <c r="D277" s="5"/>
+      <c r="E277" s="5"/>
+      <c r="F277" s="5"/>
+    </row>
+    <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" s="11"/>
-      <c r="B278" s="11"/>
-    </row>
-    <row r="279" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B278" s="9"/>
+      <c r="C278" s="5"/>
+      <c r="D278" s="5"/>
+      <c r="E278" s="5"/>
+      <c r="F278" s="5"/>
+    </row>
+    <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" s="11"/>
-      <c r="B279" s="11"/>
-    </row>
-    <row r="280" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B279" s="9"/>
+      <c r="C279" s="5"/>
+      <c r="D279" s="5"/>
+      <c r="E279" s="5"/>
+      <c r="F279" s="5"/>
+    </row>
+    <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" s="11"/>
-      <c r="B280" s="11"/>
-    </row>
-    <row r="281" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B280" s="9"/>
+      <c r="C280" s="5"/>
+      <c r="D280" s="5"/>
+      <c r="E280" s="5"/>
+      <c r="F280" s="5"/>
+    </row>
+    <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" s="11"/>
-      <c r="B281" s="11"/>
-    </row>
-    <row r="282" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B281" s="9"/>
+      <c r="C281" s="5"/>
+      <c r="D281" s="5"/>
+      <c r="E281" s="5"/>
+      <c r="F281" s="5"/>
+    </row>
+    <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" s="11"/>
-      <c r="B282" s="11"/>
-    </row>
-    <row r="283" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B282" s="9"/>
+      <c r="C282" s="5"/>
+      <c r="D282" s="5"/>
+      <c r="E282" s="5"/>
+      <c r="F282" s="5"/>
+    </row>
+    <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" s="11"/>
-      <c r="B283" s="11"/>
-    </row>
-    <row r="284" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B283" s="9"/>
+      <c r="C283" s="5"/>
+      <c r="D283" s="5"/>
+      <c r="E283" s="5"/>
+      <c r="F283" s="5"/>
+    </row>
+    <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" s="11"/>
-      <c r="B284" s="11"/>
-    </row>
-    <row r="285" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B284" s="21"/>
+      <c r="C284" s="5"/>
+      <c r="D284" s="5"/>
+      <c r="E284" s="5"/>
+      <c r="F284" s="5"/>
+    </row>
+    <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285" s="11"/>
-      <c r="B285" s="11"/>
-    </row>
-    <row r="286" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B285" s="9"/>
+      <c r="C285" s="5"/>
+      <c r="D285" s="5"/>
+      <c r="E285" s="5"/>
+      <c r="F285" s="5"/>
+    </row>
+    <row r="286" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A286" s="11"/>
-      <c r="B286" s="11"/>
-    </row>
-    <row r="287" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B286" s="9"/>
+      <c r="C286" s="5"/>
+      <c r="D286" s="5"/>
+      <c r="E286" s="5"/>
+      <c r="F286" s="5"/>
+    </row>
+    <row r="287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A287" s="11"/>
-      <c r="B287" s="11"/>
-    </row>
-    <row r="288" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B287" s="9"/>
+      <c r="C287" s="5"/>
+      <c r="D287" s="5"/>
+      <c r="E287" s="5"/>
+      <c r="F287" s="5"/>
+    </row>
+    <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" s="11"/>
-      <c r="B288" s="11"/>
-    </row>
-    <row r="289" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B288" s="9"/>
+      <c r="C288" s="5"/>
+      <c r="D288" s="5"/>
+      <c r="E288" s="5"/>
+      <c r="F288" s="5"/>
+    </row>
+    <row r="289" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A289" s="11"/>
-      <c r="B289" s="11"/>
-    </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B289" s="9"/>
+      <c r="C289" s="5"/>
+      <c r="D289" s="5"/>
+      <c r="E289" s="5"/>
+      <c r="F289" s="5"/>
+    </row>
+    <row r="290" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A290" s="11"/>
-      <c r="B290" s="11"/>
-    </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B290" s="9"/>
+      <c r="C290" s="5"/>
+      <c r="D290" s="5"/>
+      <c r="E290" s="5"/>
+      <c r="F290" s="5"/>
+    </row>
+    <row r="291" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A291" s="11"/>
-      <c r="B291" s="11"/>
-    </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B291" s="9"/>
+      <c r="C291" s="5"/>
+      <c r="D291" s="5"/>
+      <c r="E291" s="5"/>
+      <c r="F291" s="5"/>
+    </row>
+    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A292" s="11"/>
-      <c r="B292" s="11"/>
-    </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B292" s="9"/>
+      <c r="C292" s="5"/>
+      <c r="D292" s="5"/>
+      <c r="E292" s="5"/>
+      <c r="F292" s="5"/>
+    </row>
+    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A293" s="11"/>
-      <c r="B293" s="11"/>
-    </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B293" s="9"/>
+      <c r="C293" s="5"/>
+      <c r="D293" s="5"/>
+      <c r="E293" s="5"/>
+      <c r="F293" s="5"/>
+    </row>
+    <row r="294" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A294" s="11"/>
-      <c r="B294" s="11"/>
-    </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B294" s="9"/>
+      <c r="C294" s="5"/>
+      <c r="D294" s="5"/>
+      <c r="E294" s="5"/>
+      <c r="F294" s="5"/>
+    </row>
+    <row r="295" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A295" s="11"/>
-      <c r="B295" s="11"/>
-    </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B295" s="9"/>
+      <c r="C295" s="5"/>
+      <c r="D295" s="5"/>
+      <c r="E295" s="5"/>
+      <c r="F295" s="5"/>
+    </row>
+    <row r="296" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A296" s="11"/>
-      <c r="B296" s="11"/>
-    </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B296" s="9"/>
+      <c r="C296" s="5"/>
+      <c r="D296" s="5"/>
+      <c r="E296" s="5"/>
+      <c r="F296" s="5"/>
+    </row>
+    <row r="297" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A297" s="11"/>
-      <c r="B297" s="11"/>
-    </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B297" s="9"/>
+      <c r="C297" s="5"/>
+      <c r="D297" s="5"/>
+      <c r="E297" s="5"/>
+      <c r="F297" s="5"/>
+    </row>
+    <row r="298" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A298" s="11"/>
-      <c r="B298" s="11"/>
-    </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B298" s="9"/>
+      <c r="C298" s="5"/>
+      <c r="D298" s="5"/>
+      <c r="E298" s="5"/>
+      <c r="F298" s="5"/>
+    </row>
+    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A299" s="11"/>
-      <c r="B299" s="11"/>
-    </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A300" s="5" t="s">
+      <c r="B299" s="9"/>
+      <c r="C299" s="5"/>
+      <c r="D299" s="5"/>
+      <c r="E299" s="5"/>
+      <c r="F299" s="5"/>
+    </row>
+    <row r="300" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A300" s="10" t="s">
         <v>10</v>
       </c>
       <c r="B300" s="5">
         <f>SUM(B6:B299)</f>
-        <v>66</v>
+        <v>140</v>
       </c>
       <c r="C300" s="5">
         <f>SUM(C6:C299)</f>
-        <v>76</v>
+        <v>119</v>
       </c>
       <c r="D300" s="5"/>
       <c r="E300" s="5">
-        <f t="shared" ref="E300:F300" si="0">SUM(E6:E299)</f>
-        <v>412</v>
+        <f t="shared" ref="E300:I300" si="1">SUM(E6:E299)</f>
+        <v>524</v>
       </c>
       <c r="F300" s="5">
-        <f t="shared" si="0"/>
-        <v>229</v>
+        <f t="shared" si="1"/>
+        <v>311</v>
+      </c>
+      <c r="G300" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H300" s="5">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="I300" s="5">
+        <f t="shared" si="1"/>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
